--- a/ExcelTable/String.xlsx
+++ b/ExcelTable/String.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\BoardGame\ExcelTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7429E247-7BAC-40E9-A953-06942A57D7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E597B7B2-2D2B-4BBD-92C0-A07F59DC0E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="28800" windowHeight="15460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="3765" windowWidth="20310" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -92,10 +92,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이미 로그인 중입니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>인원이 부족해 시작이 불가능합니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -112,10 +108,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Already logged in</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Failed to create room</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -282,6 +274,14 @@
   </si>
   <si>
     <t>Refresh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Another user has logged into your account</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다른 기기에서 로그인되었습니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -611,14 +611,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.58203125" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
     <col min="3" max="3" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -632,7 +632,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -640,13 +640,13 @@
         <v>1000</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1001</v>
       </c>
@@ -660,7 +660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1002</v>
       </c>
@@ -671,10 +671,10 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1003</v>
       </c>
@@ -685,10 +685,10 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1004</v>
       </c>
@@ -699,10 +699,10 @@
         <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1005</v>
       </c>
@@ -710,13 +710,13 @@
         <v>1005</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1006</v>
       </c>
@@ -724,13 +724,13 @@
         <v>1006</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1007</v>
       </c>
@@ -738,13 +738,13 @@
         <v>1007</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1008</v>
       </c>
@@ -752,13 +752,13 @@
         <v>1008</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1009</v>
       </c>
@@ -766,13 +766,13 @@
         <v>1009</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1010</v>
       </c>
@@ -780,13 +780,13 @@
         <v>1010</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1011</v>
       </c>
@@ -794,13 +794,13 @@
         <v>1011</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1012</v>
       </c>
@@ -808,13 +808,13 @@
         <v>1012</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1013</v>
       </c>
@@ -822,13 +822,13 @@
         <v>1013</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1014</v>
       </c>
@@ -836,13 +836,13 @@
         <v>1014</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1015</v>
       </c>
@@ -850,13 +850,13 @@
         <v>1015</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1016</v>
       </c>
@@ -864,13 +864,13 @@
         <v>1016</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1017</v>
       </c>
@@ -878,13 +878,13 @@
         <v>1017</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1018</v>
       </c>
@@ -892,13 +892,13 @@
         <v>1018</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1019</v>
       </c>
@@ -906,13 +906,13 @@
         <v>1019</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1020</v>
       </c>
@@ -920,13 +920,13 @@
         <v>1020</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1021</v>
       </c>
@@ -934,13 +934,13 @@
         <v>1021</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1022</v>
       </c>
@@ -948,13 +948,13 @@
         <v>1022</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1023</v>
       </c>
@@ -962,13 +962,13 @@
         <v>1023</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1024</v>
       </c>
@@ -976,13 +976,13 @@
         <v>1024</v>
       </c>
       <c r="C26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" t="s">
         <v>56</v>
       </c>
-      <c r="D26" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1025</v>
       </c>
@@ -990,13 +990,13 @@
         <v>1025</v>
       </c>
       <c r="C27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" t="s">
         <v>57</v>
       </c>
-      <c r="D27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1026</v>
       </c>
@@ -1004,13 +1004,13 @@
         <v>1026</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1027</v>
       </c>
@@ -1018,13 +1018,13 @@
         <v>1027</v>
       </c>
       <c r="C29" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1028</v>
       </c>
@@ -1032,13 +1032,13 @@
         <v>1028</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1029</v>
       </c>
@@ -1046,10 +1046,10 @@
         <v>1029</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D31" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1062,12 +1062,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2181B41-2634-4EEE-8310-849A71C5CE68}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
